--- a/indoor_topology/debug_output/debug_roomself.xlsx
+++ b/indoor_topology/debug_output/debug_roomself.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,46 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -527,6 +567,26 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>41</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -560,6 +620,38 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>32</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>80</v>
+      </c>
+      <c r="U3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -601,6 +693,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +762,26 @@
       <c r="M5" t="n">
         <v>41</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>41</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -691,6 +823,26 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>194</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>41</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -724,6 +876,26 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>41</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -757,6 +929,26 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>19</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -782,6 +974,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -815,6 +1015,26 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>19</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -840,6 +1060,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -865,6 +1093,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -898,6 +1134,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -947,6 +1191,26 @@
       <c r="M14" t="n">
         <v>45</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>39</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -996,6 +1260,26 @@
       <c r="M15" t="n">
         <v>39</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>39</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1037,6 +1321,38 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>41</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>84</v>
+      </c>
+      <c r="U16" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1062,6 +1378,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1095,6 +1419,26 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>41</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1128,6 +1472,26 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>41</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
